--- a/athletics-application-template.xlsx
+++ b/athletics-application-template.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -480,8 +480,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -491,7 +493,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>순</t>
@@ -524,15 +526,26 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>참가유형
+(숙박/1일)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>희망 날짜·기간</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>참가종목1</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>참가종목2</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>참가종목3</t>
         </is>
@@ -569,15 +582,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>숙박형</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>11.9(월)~11.10(화)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>100m</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>계주</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -591,6 +614,8 @@
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -604,6 +629,8 @@
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -617,6 +644,8 @@
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -630,6 +659,8 @@
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -643,6 +674,8 @@
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -656,6 +689,8 @@
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -669,6 +704,8 @@
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -682,6 +719,8 @@
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="n">
@@ -695,6 +734,8 @@
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -708,6 +749,8 @@
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="n">
@@ -721,6 +764,8 @@
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -734,6 +779,8 @@
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="n">
@@ -747,6 +794,8 @@
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -760,6 +809,8 @@
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -773,6 +824,8 @@
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -786,6 +839,8 @@
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -799,6 +854,8 @@
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -812,6 +869,8 @@
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -825,6 +884,8 @@
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -838,6 +899,8 @@
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="n">
@@ -851,6 +914,8 @@
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="n">
@@ -864,6 +929,8 @@
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -877,6 +944,8 @@
       <c r="G27" s="5" t="n"/>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="n">
@@ -890,6 +959,8 @@
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="n">
@@ -903,6 +974,8 @@
       <c r="G29" s="5" t="n"/>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -916,6 +989,8 @@
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="n">
@@ -929,6 +1004,8 @@
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -942,6 +1019,8 @@
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="n">
@@ -955,32 +1034,29 @@
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-    </row>
-    <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>작성 안내: 참가유형은 '숙박형' 또는 '1일 왕복형' 중 기재. 참가종목은 100m, 200m, 400m, 800m, 1500m, 3000m, 계주, 멀리뛰기, 높이뛰기, 포환던지기 등 실제 참가 종목명을 기재. 1인당 최대 3종목까지 참가종목1~3에 기재. 행 추가 외 서식 변경 금지.</t>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>작성 안내: 참가유형(숙박/1일)과 희망 날짜·기간은 셀을 클릭하면 나타나는 드롭다운에서 선택하세요. 참가종목은 100m, 200m, 400m, 800m, 1500m, 3000m, 계주, 멀리뛰기, 높이뛰기, 포환던지기 등 실제 참가 종목명을 기재. 1인당 최대 3종목까지 참가종목1~3에 기재. 행 추가 외 서식 변경 금지.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A35:K35"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="G4:G33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 입력" error="숙박형 또는 1일형 중에서 선택해 주세요." type="list">
+      <formula1>"숙박형,1일형"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H4:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 입력" error="목록에 있는 날짜·기간 중에서 선택해 주세요." type="list">
+      <formula1>"11.9(월),11.10(화),11.11(수),11.12(목),11.9(월)~11.10(화),11.10(화)~11.11(수),11.11(수)~11.12(목),11.9(월)~11.11(수) 전체,11.10(화)~11.12(목) 전체"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>